--- a/ksoft_old/docs/records/Nota_Fiscal_Enum_Status.xlsx
+++ b/ksoft_old/docs/records/Nota_Fiscal_Enum_Status.xlsx
@@ -1016,13 +1016,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EB9C41F8-BE74-4930-B759-20D5CB76EE8A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B561CF8-67DC-4957-AD49-DD81AF88DEBA}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE975F0F-3C63-450A-BC89-BE8BD3CBCF4D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B9CC5622-B3EE-491E-8145-8C9EEDD1F385}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{177FFCC2-F724-470A-8D2D-EB04CFE70BFF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EDC70C94-D933-4C2B-8F90-025DB2571C26}"/>
 </file>
--- a/ksoft_old/docs/records/Nota_Fiscal_Enum_Status.xlsx
+++ b/ksoft_old/docs/records/Nota_Fiscal_Enum_Status.xlsx
@@ -1016,13 +1016,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B561CF8-67DC-4957-AD49-DD81AF88DEBA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97B200CD-10D6-45F6-9073-9B9F54058C99}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B9CC5622-B3EE-491E-8145-8C9EEDD1F385}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{34C6306C-843F-45A0-AEB2-225EBA852A2E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EDC70C94-D933-4C2B-8F90-025DB2571C26}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D1358C89-76BD-4AF7-BE14-E3FD2F6878C9}"/>
 </file>
--- a/ksoft_old/docs/records/Nota_Fiscal_Enum_Status.xlsx
+++ b/ksoft_old/docs/records/Nota_Fiscal_Enum_Status.xlsx
@@ -1016,13 +1016,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97B200CD-10D6-45F6-9073-9B9F54058C99}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EB9C41F8-BE74-4930-B759-20D5CB76EE8A}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{34C6306C-843F-45A0-AEB2-225EBA852A2E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE975F0F-3C63-450A-BC89-BE8BD3CBCF4D}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D1358C89-76BD-4AF7-BE14-E3FD2F6878C9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{177FFCC2-F724-470A-8D2D-EB04CFE70BFF}"/>
 </file>